--- a/sortivia/plantilla/Ejemplo_SORTIVIA.xlsx
+++ b/sortivia/plantilla/Ejemplo_SORTIVIA.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -631,24 +631,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Lo que va entre corchetes no forma parte del identificador: «de novo [SPAdes, Flye]» → de-novo. Úsalo para los programas o ejemplos que cambian con el tiempo: puedes actualizarlos sin tocar las reglas. Cambiar el resto del texto en inglés sí cambia el identificador.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>5. Convertir y proponer</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Profesorado autorizado: abre el panel de SORTIVIA → «Crear actividad desde Excel» → carga este archivo. El panel la revisa, calcula la estrategia óptima y la guarda como borrador; pruébala y pulsa «Proponer».</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Profesorado autorizado: abre el panel de SORTIVIA → «Crear actividad desde Excel» → carga este archivo. El panel la revisa, calcula la estrategia óptima y la guarda como borrador; pruébala y pulsa «Proponer».</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Sin cuenta: envía el Excel desde la página «Proponer una actividad» (GitHub o correo). Se revisa, se publica y se acredita a su autor.</t>
         </is>

--- a/sortivia/plantilla/Ejemplo_SORTIVIA.xlsx
+++ b/sortivia/plantilla/Ejemplo_SORTIVIA.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -498,164 +498,178 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>presupuesto: euros disponibles. rondas: intentos de sorteo. numeros: números del sorteo (1..N). puntos_por_numero: 10 → 87 puntos dan 8 números.</t>
+          <t>asignatura (opcional): sigla de la asignatura para la que está pensada; el panel agrupa las actividades por ella.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>puntos_objetivo: puntos que obtendrá la mejor estrategia posible dentro del presupuesto (el panel la calcula y reescala el resto en proporción). Recomendado: 99 (9 de 10 números).</t>
+          <t>unidad_es / unidad_en (opcionales): si el límite no es dinero, su unidad como singular|plural (p. ej., día|días y day|days).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>presupuesto: euros disponibles. rondas: intentos de sorteo. numeros: números del sorteo (1..N). puntos_por_numero: 10 → 87 puntos dan 8 números.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>puntos_objetivo: puntos que obtendrá la mejor estrategia posible dentro del presupuesto (el panel la calcula y reescala el resto en proporción). Recomendado: 99 (9 de 10 números).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>bloques_obligatorios: bloques que todos los grupos deben completar, separados por ; (por ejemplo, el diseño experimental).</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>2. Bloques (opcional, pero recomendado)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Una fila por bloque: nombre (EN), nombre (ES), objetivo (EN) y objetivo (ES). Los bloques que comparten objetivo compiten entre sí: solo cuenta el que más puntúa (p. ej., genómica y metagenómica para «Genoma»), pero los errores de cualquier bloque restan siempre.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>3. Opciones (una fila por opción)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Bloque y Decisión agrupan las opciones (mismo texto = misma decisión). Grupo (opcional) solo sirve para agrupar visualmente opciones dentro de una decisión.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Selección: «única» (una sola opción) o «múltiple» (varias). En las múltiples cuenta la mejor opción positiva y restan todas las negativas.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Tipo de coste: réplicas (la Opción es el número de réplicas; Precio = coste extra por réplica, normalmente 0) · por muestra (se paga en cada réplica y condición) · multiplicador (p. ej., x1.5, multiplica el coste por muestra: profundidad) · fijo (se paga una vez) · por unidad (contador: el grupo elige cuántas, p. ej., validaciones) · condiciones (en Precio va el número de condiciones: 1 = solo problema, 2 = problema y control).</t>
+          <t>Bloque y Decisión agrupan las opciones (mismo texto = misma decisión). Grupo (opcional) solo sirve para agrupar visualmente opciones dentro de una decisión.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Coste de cada bloque = condiciones × réplicas × (suma de precios por muestra) × multiplicadores + fijos + unidades × precio por unidad.</t>
+          <t>Selección: «única» (una sola opción) o «múltiple» (varias). En las múltiples cuenta la mejor opción positiva y restan todas las negativas.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>Tipo de coste: réplicas (la Opción es el número de réplicas; Precio = coste extra por réplica, normalmente 0) · por muestra (se paga en cada réplica y condición) · multiplicador (p. ej., x1.5, multiplica el coste por muestra: profundidad) · fijo (se paga una vez) · por unidad (contador: el grupo elige cuántas, p. ej., validaciones) · condiciones (en Precio va el número de condiciones: 1 = solo problema, 2 = problema y control).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Coste de cada bloque = condiciones × réplicas × (suma de precios por muestra) × multiplicadores + fijos + unidades × precio por unidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>Puntos: cuánto suma (o resta) elegir esa opción. Usa negativos para las trampas.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>4. Reglas de coherencia (opcional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Suman o restan puntos cuando se da una combinación. La condición se escribe con los identificadores (en minúsculas, sin tildes, con guiones), unidos con &amp;:</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   bloque  → el bloque está incluido ·  !bloque → no está incluido</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   bloque/decision=opcion  (o =opcion1|opcion2) → se ha elegido esa opción ·  bloque/decision&gt;N → contador mayor que N</t>
+          <t>Suman o restan puntos cuando se da una combinación. La condición se escribe con los identificadores (en minúsculas, sin tildes, con guiones), unidos con &amp;:</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Ejemplo: metabolomics &amp; sampling-design/design=problem-only   (metabolómica sin lago control)</t>
+          <t xml:space="preserve">   bloque  → el bloque está incluido ·  !bloque → no está incluido</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Bloque (opcional): si la regla pertenece a un bloque, sus puntos se suman a ese bloque (y solo cuentan si ese bloque es el que cuenta en su objetivo).</t>
+          <t xml:space="preserve">   bloque/decision=opcion  (o =opcion1|opcion2) → se ha elegido esa opción ·  bloque/decision&gt;N → contador mayor que N</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>El identificador de un texto es: minúsculas, sin tildes, y cualquier cosa que no sea letra o número se convierte en guion. «Problem vs control lake» → problem-vs-control-lake.</t>
+          <t xml:space="preserve">   Ejemplo: metabolomics &amp; sampling-design/design=problem-only   (metabolómica sin lago control)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>Bloque (opcional): si la regla pertenece a un bloque, sus puntos se suman a ese bloque (y solo cuentan si ese bloque es el que cuenta en su objetivo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>El identificador de un texto es: minúsculas, sin tildes, y cualquier cosa que no sea letra o número se convierte en guion. «Problem vs control lake» → problem-vs-control-lake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>Lo que va entre corchetes no forma parte del identificador: «de novo [SPAdes, Flye]» → de-novo. Úsalo para los programas o ejemplos que cambian con el tiempo: puedes actualizarlos sin tocar las reglas. Cambiar el resto del texto en inglés sí cambia el identificador.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>5. Convertir y proponer</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Profesorado autorizado: abre el panel de SORTIVIA → «Crear actividad desde Excel» → carga este archivo. El panel la revisa, calcula la estrategia óptima y la guarda como borrador; pruébala y pulsa «Proponer».</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Sin cuenta: envía el Excel desde la página «Proponer una actividad» (GitHub o correo). Se revisa, se publica y se acredita a su autor.</t>
         </is>
@@ -672,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -717,25 +731,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>titulo_es</t>
+          <t>asignatura</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>El misterio del lago verde</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr"/>
+          <t>Ejemplo</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Opcional: sigla de la asignatura (p. ej., BMSi, BAyB). Solo organiza las actividades en el panel; los grupos no la ven</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>titulo_en</t>
+          <t>titulo_es</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>The green lake mystery</t>
+          <t>El misterio del lago verde</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr"/>
@@ -743,82 +761,80 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>resumen_es</t>
+          <t>titulo_en</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>El lago se ha vuelto verde y huele mal. Diseñad la estrategia ómica que explique quién vive ahí y qué está haciendo, sin pasaros del presupuesto.</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Lo leen los grupos al entrar</t>
-        </is>
-      </c>
+          <t>The green lake mystery</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>resumen_en</t>
+          <t>resumen_es</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>The lake has turned green and smells bad. Design the omics strategy that explains who lives there and what they are doing, within budget.</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr"/>
+          <t>El lago se ha vuelto verde y huele mal. Diseñad la estrategia ómica que explique quién vive ahí y qué está haciendo, sin pasaros del presupuesto.</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Lo leen los grupos al entrar</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>presupuesto</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>€</t>
-        </is>
-      </c>
+          <t>resumen_en</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>The lake has turned green and smells bad. Design the omics strategy that explains who lives there and what they are doing, within budget.</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rondas</t>
+          <t>presupuesto</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2</v>
+        <v>3000</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Intentos de sorteo</t>
+          <t>€</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>numeros</t>
+          <t>rondas</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Números del sorteo (1..N)</t>
+          <t>Intentos de sorteo</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>puntos_por_numero</t>
+          <t>numeros</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -826,37 +842,52 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>87 puntos → 8 números</t>
+          <t>Números del sorteo (1..N)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>puntos_objetivo</t>
+          <t>puntos_por_numero</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Puntos de la mejor estrategia posible dentro del presupuesto</t>
+          <t>87 puntos → 8 números</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>puntos_objetivo</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Puntos de la mejor estrategia posible dentro del presupuesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>bloques_obligatorios</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Sampling design</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Nombres de bloque (EN) separados por ;</t>
         </is>

--- a/sortivia/plantilla/Ejemplo_SORTIVIA.xlsx
+++ b/sortivia/plantilla/Ejemplo_SORTIVIA.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -512,164 +512,171 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>presupuesto: euros disponibles. rondas: intentos de sorteo. numeros: números del sorteo (1..N). puntos_por_numero: 10 → 87 puntos dan 8 números.</t>
+          <t>limite2 / unidad2_es / unidad2_en (opcionales): un segundo límite a la vez (p. ej., 120 y min|min). Su coste va en una columna de Opciones titulada «Tiempo» o «Coste 2».</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>puntos_objetivo: puntos que obtendrá la mejor estrategia posible dentro del presupuesto (el panel la calcula y reescala el resto en proporción). Recomendado: 99 (9 de 10 números).</t>
+          <t>presupuesto: euros disponibles. rondas: intentos de sorteo. numeros: números del sorteo (1..N). puntos_por_numero: 10 → 87 puntos dan 8 números.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>puntos_objetivo: puntos que obtendrá la mejor estrategia posible dentro del presupuesto (el panel la calcula y reescala el resto en proporción). Recomendado: 99 (9 de 10 números).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>bloques_obligatorios: bloques que todos los grupos deben completar, separados por ; (por ejemplo, el diseño experimental).</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>2. Bloques (opcional, pero recomendado)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Una fila por bloque: nombre (EN), nombre (ES), objetivo (EN) y objetivo (ES). Los bloques que comparten objetivo compiten entre sí: solo cuenta el que más puntúa (p. ej., genómica y metagenómica para «Genoma»), pero los errores de cualquier bloque restan siempre.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-    </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>3. Opciones (una fila por opción)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Bloque y Decisión agrupan las opciones (mismo texto = misma decisión). Grupo (opcional) solo sirve para agrupar visualmente opciones dentro de una decisión.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Selección: «única» (una sola opción) o «múltiple» (varias). En las múltiples cuenta la mejor opción positiva y restan todas las negativas.</t>
+          <t>Bloque y Decisión agrupan las opciones (mismo texto = misma decisión). Grupo (opcional) solo sirve para agrupar visualmente opciones dentro de una decisión.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Tipo de coste: réplicas (la Opción es el número de réplicas; Precio = coste extra por réplica, normalmente 0) · por muestra (se paga en cada réplica y condición) · multiplicador (p. ej., x1.5, multiplica el coste por muestra: profundidad) · fijo (se paga una vez) · por unidad (contador: el grupo elige cuántas, p. ej., validaciones) · condiciones (en Precio va el número de condiciones: 1 = solo problema, 2 = problema y control).</t>
+          <t>Selección: «única» (una sola opción) o «múltiple» (varias). En las múltiples cuenta la mejor opción positiva y restan todas las negativas.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Coste de cada bloque = condiciones × réplicas × (suma de precios por muestra) × multiplicadores + fijos + unidades × precio por unidad.</t>
+          <t>Tipo de coste: réplicas (la Opción es el número de réplicas; Precio = coste extra por réplica, normalmente 0) · por muestra (se paga en cada réplica y condición) · multiplicador (p. ej., x1.5, multiplica el coste por muestra: profundidad) · fijo (se paga una vez) · por unidad (contador: el grupo elige cuántas, p. ej., validaciones) · condiciones (en Precio va el número de condiciones: 1 = solo problema, 2 = problema y control).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>Coste de cada bloque = condiciones × réplicas × (suma de precios por muestra) × multiplicadores + fijos + unidades × precio por unidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>Puntos: cuánto suma (o resta) elegir esa opción. Usa negativos para las trampas.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-    </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>4. Reglas de coherencia (opcional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Suman o restan puntos cuando se da una combinación. La condición se escribe con los identificadores (en minúsculas, sin tildes, con guiones), unidos con &amp;:</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   bloque  → el bloque está incluido ·  !bloque → no está incluido</t>
+          <t>Suman o restan puntos cuando se da una combinación. La condición se escribe con los identificadores (en minúsculas, sin tildes, con guiones), unidos con &amp;:</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   bloque/decision=opcion  (o =opcion1|opcion2) → se ha elegido esa opción ·  bloque/decision&gt;N → contador mayor que N</t>
+          <t xml:space="preserve">   bloque  → el bloque está incluido ·  !bloque → no está incluido</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Ejemplo: metabolomics &amp; sampling-design/design=problem-only   (metabolómica sin lago control)</t>
+          <t xml:space="preserve">   bloque/decision=opcion  (o =opcion1|opcion2) → se ha elegido esa opción ·  bloque/decision&gt;N → contador mayor que N</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Bloque (opcional): si la regla pertenece a un bloque, sus puntos se suman a ese bloque (y solo cuentan si ese bloque es el que cuenta en su objetivo).</t>
+          <t xml:space="preserve">   Ejemplo: metabolomics &amp; sampling-design/design=problem-only   (metabolómica sin lago control)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>El identificador de un texto es: minúsculas, sin tildes, y cualquier cosa que no sea letra o número se convierte en guion. «Problem vs control lake» → problem-vs-control-lake.</t>
+          <t>Bloque (opcional): si la regla pertenece a un bloque, sus puntos se suman a ese bloque (y solo cuentan si ese bloque es el que cuenta en su objetivo).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>El identificador de un texto es: minúsculas, sin tildes, y cualquier cosa que no sea letra o número se convierte en guion. «Problem vs control lake» → problem-vs-control-lake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>Lo que va entre corchetes no forma parte del identificador: «de novo [SPAdes, Flye]» → de-novo. Úsalo para los programas o ejemplos que cambian con el tiempo: puedes actualizarlos sin tocar las reglas. Cambiar el resto del texto en inglés sí cambia el identificador.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
-    </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>5. Convertir y proponer</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Profesorado autorizado: abre el panel de SORTIVIA → «Crear actividad desde Excel» → carga este archivo. El panel la revisa, calcula la estrategia óptima y la guarda como borrador; pruébala y pulsa «Proponer».</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Profesorado autorizado: abre el panel de SORTIVIA → «Crear actividad desde Excel» → carga este archivo. El panel la revisa, calcula la estrategia óptima y la guarda como borrador; pruébala y pulsa «Proponer».</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Sin cuenta: envía el Excel desde la página «Proponer una actividad» (GitHub o correo). Se revisa, se publica y se acredita a su autor.</t>
         </is>
